--- a/performance_data/train/metrics.xlsx
+++ b/performance_data/train/metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,21 +469,6 @@
           <t>rmse_vcell_spme_plus_blend</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>rmse_vcell_spme_plus_0p</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>rmse_vcell_spme_plus_0p_Ds</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>rmse_vcell_spme_plus_1p</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -503,28 +488,19 @@
         <v>21.22123724454081</v>
       </c>
       <c r="E2" t="n">
-        <v>2.317699711664766</v>
+        <v>4.625605870490952</v>
       </c>
       <c r="F2" t="n">
-        <v>4.375943915290863</v>
+        <v>4.895740558220404</v>
       </c>
       <c r="G2" t="n">
-        <v>2.327808428396418</v>
+        <v>2.369424176149481</v>
       </c>
       <c r="H2" t="n">
-        <v>5.699459547330306</v>
+        <v>5.844713328154592</v>
       </c>
       <c r="I2" t="n">
-        <v>2.157286796496949</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.321439165495549</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.87360113329509</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.237156787026669</v>
+        <v>3.355065017118853</v>
       </c>
     </row>
     <row r="3">
@@ -545,28 +521,19 @@
         <v>15.81499802423164</v>
       </c>
       <c r="E3" t="n">
-        <v>1.91445810127791</v>
+        <v>3.121145624179323</v>
       </c>
       <c r="F3" t="n">
-        <v>2.701039300465589</v>
+        <v>2.997431168602738</v>
       </c>
       <c r="G3" t="n">
-        <v>1.82350450904686</v>
+        <v>1.783975300118963</v>
       </c>
       <c r="H3" t="n">
-        <v>3.908095479769697</v>
+        <v>4.066094669817626</v>
       </c>
       <c r="I3" t="n">
-        <v>1.654163636732934</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.762214373227423</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.138831244047228</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.72718086506371</v>
+        <v>2.429635953974176</v>
       </c>
     </row>
     <row r="4">
@@ -587,28 +554,19 @@
         <v>10.43460529613702</v>
       </c>
       <c r="E4" t="n">
-        <v>1.217601937778587</v>
+        <v>1.755726104705214</v>
       </c>
       <c r="F4" t="n">
-        <v>1.394245355182985</v>
+        <v>1.528431811976807</v>
       </c>
       <c r="G4" t="n">
-        <v>1.104207779397767</v>
+        <v>1.115342161543656</v>
       </c>
       <c r="H4" t="n">
-        <v>2.243592670145958</v>
+        <v>2.385241638102423</v>
       </c>
       <c r="I4" t="n">
-        <v>1.121078866426767</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.107929294448454</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.6007924799436479</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.094709337178077</v>
+        <v>1.448271159944063</v>
       </c>
     </row>
     <row r="5">
@@ -629,28 +587,19 @@
         <v>8.290358724578624</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9286522219317486</v>
+        <v>1.275949262318341</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9860082156977774</v>
+        <v>1.070851744310127</v>
       </c>
       <c r="G5" t="n">
-        <v>0.856952154817505</v>
+        <v>0.8576696842113485</v>
       </c>
       <c r="H5" t="n">
-        <v>1.648460712526256</v>
+        <v>1.692973118138564</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8926069134242144</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.8535001291089431</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.4338944505069599</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.8456965647224761</v>
+        <v>1.05781306482933</v>
       </c>
     </row>
     <row r="6">
@@ -671,28 +620,19 @@
         <v>6.165537630334028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6650808341374266</v>
+        <v>0.8574521631933877</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6625251440221505</v>
+        <v>0.7064240370985014</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6233862939220821</v>
+        <v>0.6203802832026593</v>
       </c>
       <c r="H6" t="n">
-        <v>1.118054837621196</v>
+        <v>1.092647549163039</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6468389616705514</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.6186871375612298</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.2914493832879435</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.6148650700974513</v>
+        <v>0.7200935716215007</v>
       </c>
     </row>
     <row r="7">
@@ -713,28 +653,19 @@
         <v>4.07202828432913</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4290565447727026</v>
+        <v>0.5077604493521536</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4100382680442112</v>
+        <v>0.4251131906052733</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4086725912827315</v>
+        <v>0.4051530748505767</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6566933520451094</v>
+        <v>0.612842498155045</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4206143841801883</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.4047681079892214</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.1729493375017775</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.4033576180680953</v>
+        <v>0.442404097955402</v>
       </c>
     </row>
     <row r="8">
@@ -755,28 +686,19 @@
         <v>2.02038426290311</v>
       </c>
       <c r="E8" t="n">
-        <v>0.212723155879439</v>
+        <v>0.2280054305836261</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2015818499137469</v>
+        <v>0.2030936814202387</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2076643487212065</v>
+        <v>0.2053122511345286</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2729801449459152</v>
+        <v>0.2535524843937741</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2121626751438105</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.2053442792808798</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.08060349957380911</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.2050192419526497</v>
+        <v>0.2127100297809116</v>
       </c>
     </row>
     <row r="9">
@@ -797,28 +719,19 @@
         <v>1.962748419969131</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1836422659581957</v>
+        <v>0.2239327889117262</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1896592290244461</v>
+        <v>0.1891026104808614</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1836667855790995</v>
+        <v>0.1892491059297635</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2294463818320825</v>
+        <v>0.2763594654686935</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1867621590620124</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1890784383269578</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.05862561144389828</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.1889492368222945</v>
+        <v>0.1975633689623738</v>
       </c>
     </row>
     <row r="10">
@@ -839,28 +752,19 @@
         <v>3.921529491973721</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4059749893125004</v>
+        <v>0.6779825829434512</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4031346991277136</v>
+        <v>0.3997809414921012</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3889429545330468</v>
+        <v>0.4138304560533122</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6109908979805229</v>
+        <v>1.040752692813373</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4060564570965113</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.4135084173832952</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.1820573701895047</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.4115881445501066</v>
+        <v>0.4820741846058023</v>
       </c>
     </row>
     <row r="11">
@@ -881,28 +785,19 @@
         <v>5.876202108423684</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7489213990695858</v>
+        <v>1.499538152847273</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6707006030336682</v>
+        <v>0.6671853975814248</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6602983911515836</v>
+        <v>0.7218569491531931</v>
       </c>
       <c r="H11" t="n">
-        <v>1.193764087711966</v>
+        <v>2.531440790422235</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7084106930458179</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.7225637207460811</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.3983379633326937</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.716240546057895</v>
+        <v>0.9368495777656951</v>
       </c>
     </row>
     <row r="12">
@@ -923,28 +818,19 @@
         <v>7.827034170237597</v>
       </c>
       <c r="E12" t="n">
-        <v>1.299954143661912</v>
+        <v>2.724536155573142</v>
       </c>
       <c r="F12" t="n">
-        <v>1.018528623985213</v>
+        <v>1.021546759357178</v>
       </c>
       <c r="G12" t="n">
-        <v>1.044153795457932</v>
+        <v>1.158645449236248</v>
       </c>
       <c r="H12" t="n">
-        <v>1.995960347918118</v>
+        <v>4.668567893373048</v>
       </c>
       <c r="I12" t="n">
-        <v>1.14783620259955</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.162560850920677</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.7459247068416586</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.149495608508981</v>
+        <v>1.617794784771335</v>
       </c>
     </row>
     <row r="13">
@@ -965,28 +851,19 @@
         <v>9.775195362383183</v>
       </c>
       <c r="E13" t="n">
-        <v>2.127688766316358</v>
+        <v>4.24606094878276</v>
       </c>
       <c r="F13" t="n">
-        <v>1.469564055386743</v>
+        <v>1.485002651759886</v>
       </c>
       <c r="G13" t="n">
-        <v>1.580593352348253</v>
+        <v>1.759643154137721</v>
       </c>
       <c r="H13" t="n">
-        <v>3.022117712195</v>
+        <v>7.283275419479653</v>
       </c>
       <c r="I13" t="n">
-        <v>1.769568189552206</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.769164754205304</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.259752287571039</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.747736045910468</v>
+        <v>2.31366373532355</v>
       </c>
     </row>
     <row r="14">
@@ -1007,28 +884,19 @@
         <v>14.64175996943092</v>
       </c>
       <c r="E14" t="n">
-        <v>5.525236149328594</v>
+        <v>9.292304614256599</v>
       </c>
       <c r="F14" t="n">
-        <v>3.210008964713404</v>
+        <v>3.264251710549037</v>
       </c>
       <c r="G14" t="n">
-        <v>3.782042434107241</v>
+        <v>4.145835279417661</v>
       </c>
       <c r="H14" t="n">
-        <v>6.299024978993507</v>
+        <v>16.1363205068077</v>
       </c>
       <c r="I14" t="n">
-        <v>4.300105295404981</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.177414288260673</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.445863945740046</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4.131900654307509</v>
+        <v>5.338380670068159</v>
       </c>
     </row>
     <row r="15">
@@ -1049,28 +917,19 @@
         <v>19.53403585107847</v>
       </c>
       <c r="E15" t="n">
-        <v>11.40439252980913</v>
+        <v>16.75176937874921</v>
       </c>
       <c r="F15" t="n">
-        <v>6.420007388469299</v>
+        <v>6.50250589732762</v>
       </c>
       <c r="G15" t="n">
-        <v>7.758948459438805</v>
+        <v>8.149657784510444</v>
       </c>
       <c r="H15" t="n">
-        <v>11.36272066307435</v>
+        <v>27.95146995154373</v>
       </c>
       <c r="I15" t="n">
-        <v>8.644792188188914</v>
-      </c>
-      <c r="J15" t="n">
-        <v>8.208088790308013</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7.286273686114878</v>
-      </c>
-      <c r="L15" t="n">
-        <v>8.140521004719538</v>
+        <v>10.44472360626766</v>
       </c>
     </row>
     <row r="16">
@@ -1091,28 +950,19 @@
         <v>6.784852717889676</v>
       </c>
       <c r="E16" t="n">
-        <v>1.077706388115884</v>
+        <v>1.324416836606523</v>
       </c>
       <c r="F16" t="n">
-        <v>1.181680675286101</v>
+        <v>1.120225888661523</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9756635627735422</v>
+        <v>1.061195724660591</v>
       </c>
       <c r="H16" t="n">
-        <v>1.485956285518721</v>
+        <v>1.538273442966369</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8354201930506631</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.027118705403577</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.6761359120066487</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.9801327605733158</v>
+        <v>1.191732308773659</v>
       </c>
     </row>
     <row r="17">
@@ -1133,28 +983,19 @@
         <v>6.585468819054708</v>
       </c>
       <c r="E17" t="n">
-        <v>1.536723072441414</v>
+        <v>1.977142280511266</v>
       </c>
       <c r="F17" t="n">
-        <v>1.258641008430351</v>
+        <v>1.130530317421723</v>
       </c>
       <c r="G17" t="n">
-        <v>1.067088374706513</v>
+        <v>1.173259615871612</v>
       </c>
       <c r="H17" t="n">
-        <v>1.240457051527312</v>
+        <v>2.9811705639115</v>
       </c>
       <c r="I17" t="n">
-        <v>1.053617753689242</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.14963362333679</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.7897218391166195</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.10980617889565</v>
+        <v>1.385050181834417</v>
       </c>
     </row>
     <row r="18">
@@ -1175,28 +1016,19 @@
         <v>6.641944901430178</v>
       </c>
       <c r="E18" t="n">
-        <v>1.305481540637845</v>
+        <v>1.310806671109706</v>
       </c>
       <c r="F18" t="n">
-        <v>1.271197456039798</v>
+        <v>1.072995823954946</v>
       </c>
       <c r="G18" t="n">
-        <v>1.017443412224184</v>
+        <v>1.100790667883333</v>
       </c>
       <c r="H18" t="n">
-        <v>1.52795941595735</v>
+        <v>1.470563576448192</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8363612982122645</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.056553335122016</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.7423610663200886</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.00490227146564</v>
+        <v>1.209592443667232</v>
       </c>
     </row>
     <row r="19">
@@ -1217,28 +1049,19 @@
         <v>6.540292866364347</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8742746677832</v>
+        <v>1.354278220656266</v>
       </c>
       <c r="F19" t="n">
-        <v>1.305729415277119</v>
+        <v>1.122410828287388</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9953590607482466</v>
+        <v>1.087102927410675</v>
       </c>
       <c r="H19" t="n">
-        <v>1.135161821162895</v>
+        <v>1.769715663900745</v>
       </c>
       <c r="I19" t="n">
-        <v>1.01669747936285</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.048176144041337</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.7388919219559877</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.000802307870558</v>
+        <v>1.145556301658547</v>
       </c>
     </row>
     <row r="20">
@@ -1259,28 +1082,19 @@
         <v>6.083672387387892</v>
       </c>
       <c r="E20" t="n">
-        <v>1.611879575912095</v>
+        <v>1.185563845864392</v>
       </c>
       <c r="F20" t="n">
-        <v>1.245855633544562</v>
+        <v>0.9883795335495331</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9899724645672869</v>
+        <v>1.051730047036348</v>
       </c>
       <c r="H20" t="n">
-        <v>1.445521264613116</v>
+        <v>1.290524620458876</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8631337230753354</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.010390029354833</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.773567386060798</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.9672070515494353</v>
+        <v>1.124599109775092</v>
       </c>
     </row>
     <row r="21">
@@ -1301,28 +1115,19 @@
         <v>6.047225485993786</v>
       </c>
       <c r="E21" t="n">
-        <v>1.948315835735743</v>
+        <v>1.123267703714955</v>
       </c>
       <c r="F21" t="n">
-        <v>1.232460745292191</v>
+        <v>1.03875874004968</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9291304292827263</v>
+        <v>1.004435576447558</v>
       </c>
       <c r="H21" t="n">
-        <v>1.099729457905631</v>
+        <v>1.335109040983142</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9941132066923044</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.9652066599321122</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.7419435942357602</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.9229925410745322</v>
+        <v>1.02252738875053</v>
       </c>
     </row>
     <row r="22">
@@ -1343,28 +1148,19 @@
         <v>5.383235943407008</v>
       </c>
       <c r="E22" t="n">
-        <v>2.401917023706118</v>
+        <v>1.350497517852365</v>
       </c>
       <c r="F22" t="n">
-        <v>1.501291325995635</v>
+        <v>1.320679677379033</v>
       </c>
       <c r="G22" t="n">
-        <v>1.335277042902793</v>
+        <v>1.31309388507226</v>
       </c>
       <c r="H22" t="n">
-        <v>1.777821504419531</v>
+        <v>1.431247825814667</v>
       </c>
       <c r="I22" t="n">
-        <v>1.771219886792939</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.330342840471005</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.257523198705864</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.351505524344528</v>
+        <v>1.322839863483278</v>
       </c>
     </row>
     <row r="23">
@@ -1385,28 +1181,19 @@
         <v>8.222222774009676</v>
       </c>
       <c r="E23" t="n">
-        <v>3.792055768363988</v>
+        <v>2.151535636731759</v>
       </c>
       <c r="F23" t="n">
-        <v>2.450212849471149</v>
+        <v>2.158614839498679</v>
       </c>
       <c r="G23" t="n">
-        <v>2.142172738841924</v>
+        <v>2.100359332844393</v>
       </c>
       <c r="H23" t="n">
-        <v>2.826512792617707</v>
+        <v>2.367562173122749</v>
       </c>
       <c r="I23" t="n">
-        <v>2.810830445760909</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.130257033197681</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.013571315373324</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.166972098962626</v>
+        <v>2.107735407114264</v>
       </c>
     </row>
   </sheetData>
